--- a/umi-max/src/pages/translate/lovepik/translate.xlsx
+++ b/umi-max/src/pages/translate/lovepik/translate.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>key</t>
   </si>
@@ -98,147 +98,70 @@
     <t>tl</t>
   </si>
   <si>
-    <t>save_off</t>
-  </si>
-  <si>
-    <t>Save {$discount} Off</t>
-  </si>
-  <si>
-    <t>{$discount}を保存します</t>
-  </si>
-  <si>
-    <t>Lưu {$discount} TẮT</t>
-  </si>
-  <si>
-    <t>{$discount}를 저장합니다</t>
-  </si>
-  <si>
-    <t>Сохранить {$discount} OFF</t>
-  </si>
-  <si>
-    <t>Salvar {$discount} off</t>
-  </si>
-  <si>
-    <t>Ahorrar {$discount}</t>
-  </si>
-  <si>
-    <t>Économisez {$discount} Off</t>
-  </si>
-  <si>
-    <t>บันทึก {$discount} ปิด</t>
-  </si>
-  <si>
-    <t>Sparen Sie {$discount} aus</t>
-  </si>
-  <si>
-    <t>Zapisz {$discount} wyłącz</t>
-  </si>
-  <si>
-    <t>Salva {$discount} off</t>
-  </si>
-  <si>
-    <t>保存 {$discount} OFF</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>{$discount} बचाओ</t>
-    </r>
-  </si>
-  <si>
-    <t>Simpan {$discount} off</t>
-  </si>
-  <si>
-    <t>Simpan {$discount} OFF</t>
-  </si>
-  <si>
-    <t>Kaydet {$discount} kapalı</t>
-  </si>
-  <si>
-    <t>Bespaar {$discount}</t>
-  </si>
-  <si>
-    <t>وفر {$discount}</t>
-  </si>
-  <si>
-    <t>{$discount} ছাড় সংরক্ষণ করুন</t>
-  </si>
-  <si>
-    <t>חסכו {$discount} הנחה</t>
-  </si>
-  <si>
-    <t>I-save ang {$discount} Off</t>
-  </si>
-  <si>
-    <t>Only</t>
-  </si>
-  <si>
-    <t>のみ</t>
-  </si>
-  <si>
-    <t>Chỉ một</t>
-  </si>
-  <si>
-    <t>오직</t>
-  </si>
-  <si>
-    <t>Только</t>
-  </si>
-  <si>
-    <t>Apenas</t>
-  </si>
-  <si>
-    <t>Solo</t>
-  </si>
-  <si>
-    <t>Seulement</t>
-  </si>
-  <si>
-    <t>เท่านั้น</t>
-  </si>
-  <si>
-    <t>Nur</t>
-  </si>
-  <si>
-    <t>Tylko</t>
-  </si>
-  <si>
-    <t>Soltanto</t>
-  </si>
-  <si>
-    <t>僅有的</t>
-  </si>
-  <si>
-    <t>केवल</t>
-  </si>
-  <si>
-    <t>Hanya</t>
-  </si>
-  <si>
-    <t>Sadece</t>
-  </si>
-  <si>
-    <t>Alleen</t>
-  </si>
-  <si>
-    <t>فقط</t>
-  </si>
-  <si>
-    <t>শুধুমাত্র</t>
-  </si>
-  <si>
-    <t>רק</t>
-  </si>
-  <si>
-    <t>Tanging</t>
+    <t>{$num} credit costed</t>
+  </si>
+  <si>
+    <t>{$num} クレジットを消費しました</t>
+  </si>
+  <si>
+    <t>{$num} tín dụng đã sử dụng</t>
+  </si>
+  <si>
+    <t>{$num} 크레딧 사용됨</t>
+  </si>
+  <si>
+    <t>{$num} кредитов потрачено</t>
+  </si>
+  <si>
+    <t>{$num} crédito gasto</t>
+  </si>
+  <si>
+    <t>{$num} crédito gastado</t>
+  </si>
+  <si>
+    <t>{$num} crédit dépensé</t>
+  </si>
+  <si>
+    <t>{$num} เครดิตที่ใช้ไป</t>
+  </si>
+  <si>
+    <t>{$num} Guthaben verbraucht</t>
+  </si>
+  <si>
+    <t>{$num} wykorzystanych kredytów</t>
+  </si>
+  <si>
+    <t>{$num} credito speso</t>
+  </si>
+  <si>
+    <t>{$num} 积分已消耗</t>
+  </si>
+  <si>
+    <t>{$num} क्रेडिट खर्च</t>
+  </si>
+  <si>
+    <t>{$num} kredit digunakan</t>
+  </si>
+  <si>
+    <t>{$num} kredit terpakai</t>
+  </si>
+  <si>
+    <t>{$num} kredi harcandı</t>
+  </si>
+  <si>
+    <t>{$num} tegoed verbruikt</t>
+  </si>
+  <si>
+    <t>{$num} رصيد مستهلك</t>
+  </si>
+  <si>
+    <t>{$num} ক্রেডিট খরচ হয়েছে</t>
+  </si>
+  <si>
+    <t>{$num} אשראי נוצל</t>
+  </si>
+  <si>
+    <t>{$num} nagastos na kredito</t>
   </si>
 </sst>
 </file>
@@ -251,7 +174,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -264,18 +187,12 @@
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF333333"/>
-      <name val="Microsoft YaHei"/>
+      <color theme="1"/>
+      <name val="var(--yb-font-body-medium)"/>
       <charset val="134"/>
     </font>
     <font>
@@ -430,7 +347,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -445,6 +362,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -630,11 +553,46 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="12">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFE0E0E0"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFE0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFE0E0E0"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFE0E0E0"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFE0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFE0E0E0"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFE0E0E0"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -741,172 +699,175 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1424,6 +1385,7 @@
   <dimension ref="A1:Z15"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="18" customHeight="1"/>
   <cols>
+    <col min="1" max="1" width="17.1979166666667" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="8" max="8" width="38.71875" customWidth="1"/>
   </cols>
@@ -1486,490 +1448,419 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="V1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="W1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="3"/>
+      <c r="X1" s="6"/>
+      <c r="Y1" s="6"/>
+      <c r="Z1" s="6"/>
     </row>
     <row r="2" customHeight="1" spans="1:26">
-      <c r="A2" t="s">
+      <c r="A2" s="2"/>
+      <c r="B2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="S2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="T2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="T2" s="5" t="s">
+      <c r="U2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="U2" s="5" t="s">
+      <c r="V2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="V2" s="5" t="s">
+      <c r="W2" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="W2" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="X2" s="6"/>
       <c r="Y2" s="6"/>
       <c r="Z2" s="6"/>
     </row>
-    <row r="3" customHeight="1" spans="2:26">
-      <c r="B3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="T3" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="U3" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="V3" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="6"/>
-    </row>
-    <row r="4" customHeight="1" spans="2:26">
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="3"/>
+    <row r="4" customHeight="1" spans="1:26">
+      <c r="A4" s="4"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+      <c r="V4" s="5"/>
+      <c r="W4" s="5"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6"/>
+      <c r="Z4" s="6"/>
     </row>
     <row r="5" customHeight="1" spans="2:26">
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="3"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="6"/>
+      <c r="T5" s="6"/>
+      <c r="U5" s="6"/>
+      <c r="V5" s="6"/>
+      <c r="W5" s="6"/>
+      <c r="X5" s="6"/>
+      <c r="Y5" s="6"/>
+      <c r="Z5" s="6"/>
     </row>
     <row r="6" customHeight="1" spans="2:26">
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
-      <c r="Y6" s="3"/>
-      <c r="Z6" s="3"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="6"/>
+      <c r="T6" s="6"/>
+      <c r="U6" s="6"/>
+      <c r="V6" s="6"/>
+      <c r="W6" s="6"/>
+      <c r="X6" s="6"/>
+      <c r="Y6" s="6"/>
+      <c r="Z6" s="6"/>
     </row>
     <row r="7" customHeight="1" spans="2:26">
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
-      <c r="Y7" s="3"/>
-      <c r="Z7" s="3"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="6"/>
+      <c r="Z7" s="6"/>
     </row>
-    <row r="8" customHeight="1" spans="2:26">
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="3"/>
+    <row r="8" customHeight="1" spans="1:26">
+      <c r="A8" s="4"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="T8" s="5"/>
+      <c r="U8" s="5"/>
+      <c r="V8" s="5"/>
+      <c r="W8" s="5"/>
+      <c r="X8" s="6"/>
+      <c r="Y8" s="6"/>
+      <c r="Z8" s="6"/>
     </row>
     <row r="9" customHeight="1" spans="2:26">
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="3"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="6"/>
+      <c r="T9" s="6"/>
+      <c r="U9" s="6"/>
+      <c r="V9" s="6"/>
+      <c r="W9" s="6"/>
+      <c r="X9" s="6"/>
+      <c r="Y9" s="6"/>
+      <c r="Z9" s="6"/>
     </row>
     <row r="10" customHeight="1" spans="2:26">
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
-      <c r="Y10" s="3"/>
-      <c r="Z10" s="3"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6"/>
+      <c r="S10" s="6"/>
+      <c r="T10" s="6"/>
+      <c r="U10" s="6"/>
+      <c r="V10" s="6"/>
+      <c r="W10" s="6"/>
+      <c r="X10" s="6"/>
+      <c r="Y10" s="6"/>
+      <c r="Z10" s="6"/>
     </row>
     <row r="11" customHeight="1" spans="2:26">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="6"/>
+      <c r="R11" s="6"/>
+      <c r="S11" s="6"/>
+      <c r="T11" s="6"/>
+      <c r="U11" s="6"/>
+      <c r="V11" s="6"/>
+      <c r="W11" s="6"/>
+      <c r="X11" s="6"/>
+      <c r="Y11" s="6"/>
+      <c r="Z11" s="6"/>
     </row>
     <row r="12" customHeight="1" spans="2:26">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
-      <c r="U12" s="3"/>
-      <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
-      <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="3"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="6"/>
+      <c r="Q12" s="6"/>
+      <c r="R12" s="6"/>
+      <c r="S12" s="6"/>
+      <c r="T12" s="6"/>
+      <c r="U12" s="6"/>
+      <c r="V12" s="6"/>
+      <c r="W12" s="6"/>
+      <c r="X12" s="6"/>
+      <c r="Y12" s="6"/>
+      <c r="Z12" s="6"/>
     </row>
     <row r="13" customHeight="1" spans="2:26">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
-      <c r="U13" s="3"/>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="3"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="6"/>
+      <c r="T13" s="6"/>
+      <c r="U13" s="6"/>
+      <c r="V13" s="6"/>
+      <c r="W13" s="6"/>
+      <c r="X13" s="6"/>
+      <c r="Y13" s="6"/>
+      <c r="Z13" s="6"/>
     </row>
     <row r="14" customHeight="1" spans="2:26">
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="3"/>
-      <c r="U14" s="3"/>
-      <c r="V14" s="3"/>
-      <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="3"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="6"/>
+      <c r="T14" s="6"/>
+      <c r="U14" s="6"/>
+      <c r="V14" s="6"/>
+      <c r="W14" s="6"/>
+      <c r="X14" s="6"/>
+      <c r="Y14" s="6"/>
+      <c r="Z14" s="6"/>
     </row>
     <row r="15" customHeight="1" spans="2:26">
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
-      <c r="T15" s="3"/>
-      <c r="U15" s="3"/>
-      <c r="V15" s="3"/>
-      <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
-      <c r="Y15" s="3"/>
-      <c r="Z15" s="3"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6"/>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="6"/>
+      <c r="S15" s="6"/>
+      <c r="T15" s="6"/>
+      <c r="U15" s="6"/>
+      <c r="V15" s="6"/>
+      <c r="W15" s="6"/>
+      <c r="X15" s="6"/>
+      <c r="Y15" s="6"/>
+      <c r="Z15" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/umi-max/src/pages/translate/lovepik/translate.xlsx
+++ b/umi-max/src/pages/translate/lovepik/translate.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>key</t>
   </si>
@@ -98,70 +98,58 @@
     <t>tl</t>
   </si>
   <si>
-    <t>{$num} credit costed</t>
-  </si>
-  <si>
-    <t>{$num} クレジットを消費しました</t>
-  </si>
-  <si>
-    <t>{$num} tín dụng đã sử dụng</t>
-  </si>
-  <si>
-    <t>{$num} 크레딧 사용됨</t>
-  </si>
-  <si>
-    <t>{$num} кредитов потрачено</t>
-  </si>
-  <si>
-    <t>{$num} crédito gasto</t>
-  </si>
-  <si>
-    <t>{$num} crédito gastado</t>
-  </si>
-  <si>
-    <t>{$num} crédit dépensé</t>
-  </si>
-  <si>
-    <t>{$num} เครดิตที่ใช้ไป</t>
-  </si>
-  <si>
-    <t>{$num} Guthaben verbraucht</t>
-  </si>
-  <si>
-    <t>{$num} wykorzystanych kredytów</t>
-  </si>
-  <si>
-    <t>{$num} credito speso</t>
-  </si>
-  <si>
-    <t>{$num} 积分已消耗</t>
-  </si>
-  <si>
-    <t>{$num} क्रेडिट खर्च</t>
-  </si>
-  <si>
-    <t>{$num} kredit digunakan</t>
-  </si>
-  <si>
-    <t>{$num} kredit terpakai</t>
-  </si>
-  <si>
-    <t>{$num} kredi harcandı</t>
-  </si>
-  <si>
-    <t>{$num} tegoed verbruikt</t>
-  </si>
-  <si>
-    <t>{$num} رصيد مستهلك</t>
-  </si>
-  <si>
-    <t>{$num} ক্রেডিট খরচ হয়েছে</t>
-  </si>
-  <si>
-    <t>{$num} אשראי נוצל</t>
-  </si>
-  <si>
-    <t>{$num} nagastos na kredito</t>
+    <t>access_to_all_premium_assets</t>
+  </si>
+  <si>
+    <t>{$duration} access sa lahat ng premium asset</t>
+  </si>
+  <si>
+    <t>get_your_free_ai_ppt</t>
+  </si>
+  <si>
+    <t>Kunin ang Iyong Libreng AI PPT</t>
+  </si>
+  <si>
+    <t>try_free</t>
+  </si>
+  <si>
+    <t>Subukan ang Libreng</t>
+  </si>
+  <si>
+    <t>one-sentence_prompt._one_perfect_presentation</t>
+  </si>
+  <si>
+    <t>Isang pangungusap na prompt. Isang perpektong presentasyon</t>
+  </si>
+  <si>
+    <t>special_offer</t>
+  </si>
+  <si>
+    <t>ESPESYAL NA ALOK!</t>
+  </si>
+  <si>
+    <t>referral_pngtree_text_1</t>
+  </si>
+  <si>
+    <t>20 milyong creative asset ang maaaring i-download nang libre.</t>
+  </si>
+  <si>
+    <t>referral_pikbest_text_1</t>
+  </si>
+  <si>
+    <t>Mas maraming template at video ang maaaring i-download nang walang limitasyon.</t>
+  </si>
+  <si>
+    <t>referral_pngtree_text_2</t>
+  </si>
+  <si>
+    <t>Kunin ang Iyong Libreng Creative Asset</t>
+  </si>
+  <si>
+    <t>referral_pikbest_text_2</t>
+  </si>
+  <si>
+    <t>Kunin ang Iyong De-kalidad na mga Template at Video</t>
   </si>
 </sst>
 </file>
@@ -174,7 +162,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -190,9 +178,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="var(--yb-font-body-medium)"/>
+      <sz val="11.25"/>
+      <color rgb="FF000000"/>
+      <name val="var(--yb-font-body-large)"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11.25"/>
+      <color rgb="FF000000"/>
+      <name val="var(--hy-font-family)"/>
       <charset val="134"/>
     </font>
     <font>
@@ -347,7 +341,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -362,12 +356,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -553,46 +541,11 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FFE0E0E0"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFE0E0E0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFE0E0E0"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFE0E0E0"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFE0E0E0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFE0E0E0"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FFE0E0E0"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -699,163 +652,160 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -863,11 +813,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1382,12 +1332,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z15"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="17.1979166666667" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="1" max="1" width="54.2916666666667" customWidth="1"/>
+    <col min="2" max="2" width="52.5520833333333" customWidth="1"/>
     <col min="8" max="8" width="38.71875" customWidth="1"/>
+    <col min="14" max="14" width="41.3541666666667" customWidth="1"/>
+    <col min="19" max="19" width="17.5208333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:26">
@@ -1448,419 +1400,309 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="U1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="W1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="6"/>
-      <c r="Z1" s="6"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
     </row>
     <row r="2" customHeight="1" spans="1:26">
-      <c r="A2" s="2"/>
-      <c r="B2" s="3" t="s">
+      <c r="A2" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
+    </row>
+    <row r="3" customHeight="1" spans="1:26">
+      <c r="A3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="V2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="W2" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="X2" s="6"/>
-      <c r="Y2" s="6"/>
-      <c r="Z2" s="6"/>
+      <c r="X3" s="2"/>
+      <c r="Y3" s="2"/>
+      <c r="Z3" s="2"/>
     </row>
     <row r="4" customHeight="1" spans="1:26">
-      <c r="A4" s="4"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
       <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
-      <c r="U4" s="5"/>
-      <c r="V4" s="5"/>
-      <c r="W4" s="5"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="6"/>
-      <c r="Z4" s="6"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
     </row>
-    <row r="5" customHeight="1" spans="2:26">
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
+    <row r="5" customHeight="1" spans="1:26">
+      <c r="A5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
       <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="6"/>
-      <c r="Z5" s="6"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
+      <c r="Z5" s="2"/>
     </row>
-    <row r="6" customHeight="1" spans="2:26">
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="6"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
+    <row r="6" customHeight="1" spans="1:26">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="2"/>
+      <c r="Z6" s="2"/>
     </row>
-    <row r="7" customHeight="1" spans="2:26">
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
+    <row r="7" customHeight="1" spans="1:26">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
       <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="6"/>
-      <c r="Z7" s="6"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="2"/>
+      <c r="Z7" s="2"/>
     </row>
     <row r="8" customHeight="1" spans="1:26">
-      <c r="A8" s="4"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
       <c r="S8" s="5"/>
-      <c r="T8" s="5"/>
-      <c r="U8" s="5"/>
-      <c r="V8" s="5"/>
-      <c r="W8" s="5"/>
-      <c r="X8" s="6"/>
-      <c r="Y8" s="6"/>
-      <c r="Z8" s="6"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+      <c r="W8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X8" s="2"/>
+      <c r="Y8" s="2"/>
+      <c r="Z8" s="2"/>
     </row>
-    <row r="9" customHeight="1" spans="2:26">
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="6"/>
-      <c r="T9" s="6"/>
-      <c r="U9" s="6"/>
-      <c r="V9" s="6"/>
-      <c r="W9" s="6"/>
-      <c r="X9" s="6"/>
-      <c r="Y9" s="6"/>
-      <c r="Z9" s="6"/>
+    <row r="9" customHeight="1" spans="1:26">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="X9" s="2"/>
+      <c r="Y9" s="2"/>
+      <c r="Z9" s="2"/>
     </row>
-    <row r="10" customHeight="1" spans="2:26">
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="6"/>
-      <c r="S10" s="6"/>
-      <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
-      <c r="V10" s="6"/>
-      <c r="W10" s="6"/>
-      <c r="X10" s="6"/>
-      <c r="Y10" s="6"/>
-      <c r="Z10" s="6"/>
-    </row>
-    <row r="11" customHeight="1" spans="2:26">
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
-      <c r="R11" s="6"/>
-      <c r="S11" s="6"/>
-      <c r="T11" s="6"/>
-      <c r="U11" s="6"/>
-      <c r="V11" s="6"/>
-      <c r="W11" s="6"/>
-      <c r="X11" s="6"/>
-      <c r="Y11" s="6"/>
-      <c r="Z11" s="6"/>
-    </row>
-    <row r="12" customHeight="1" spans="2:26">
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="6"/>
-      <c r="S12" s="6"/>
-      <c r="T12" s="6"/>
-      <c r="U12" s="6"/>
-      <c r="V12" s="6"/>
-      <c r="W12" s="6"/>
-      <c r="X12" s="6"/>
-      <c r="Y12" s="6"/>
-      <c r="Z12" s="6"/>
-    </row>
-    <row r="13" customHeight="1" spans="2:26">
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="6"/>
-      <c r="S13" s="6"/>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="6"/>
-      <c r="W13" s="6"/>
-      <c r="X13" s="6"/>
-      <c r="Y13" s="6"/>
-      <c r="Z13" s="6"/>
-    </row>
-    <row r="14" customHeight="1" spans="2:26">
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
-      <c r="R14" s="6"/>
-      <c r="S14" s="6"/>
-      <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
-      <c r="V14" s="6"/>
-      <c r="W14" s="6"/>
-      <c r="X14" s="6"/>
-      <c r="Y14" s="6"/>
-      <c r="Z14" s="6"/>
-    </row>
-    <row r="15" customHeight="1" spans="2:26">
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
-      <c r="Q15" s="6"/>
-      <c r="R15" s="6"/>
-      <c r="S15" s="6"/>
-      <c r="T15" s="6"/>
-      <c r="U15" s="6"/>
-      <c r="V15" s="6"/>
-      <c r="W15" s="6"/>
-      <c r="X15" s="6"/>
-      <c r="Y15" s="6"/>
-      <c r="Z15" s="6"/>
+    <row r="10" customHeight="1" spans="1:26">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="2"/>
+      <c r="Z10" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
